--- a/backend/data/financials_by_company/1EP.F.xlsx
+++ b/backend/data/financials_by_company/1EP.F.xlsx
@@ -692,642 +692,642 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-184468.632708</v>
+        <v>2582.437276</v>
       </c>
       <c r="C2" t="n">
-        <v>0.332976</v>
+        <v>0.234767</v>
       </c>
       <c r="D2" t="n">
-        <v>6387000</v>
+        <v>3014000</v>
       </c>
       <c r="E2" t="n">
-        <v>-554000</v>
+        <v>11000</v>
       </c>
       <c r="F2" t="n">
-        <v>-554000</v>
+        <v>11000</v>
       </c>
       <c r="G2" t="n">
-        <v>1243000</v>
+        <v>854000</v>
       </c>
       <c r="H2" t="n">
-        <v>3046000</v>
+        <v>1810000</v>
       </c>
       <c r="I2" t="n">
-        <v>12077000</v>
+        <v>7917000</v>
       </c>
       <c r="J2" t="n">
-        <v>5833000</v>
+        <v>3025000</v>
       </c>
       <c r="K2" t="n">
-        <v>2787000</v>
+        <v>1215000</v>
       </c>
       <c r="L2" t="n">
-        <v>-671000</v>
+        <v>-136000</v>
       </c>
       <c r="M2" t="n">
-        <v>922000</v>
+        <v>99000</v>
       </c>
       <c r="N2" t="n">
-        <v>292000</v>
+        <v>23000</v>
       </c>
       <c r="O2" t="n">
-        <v>1612531.367292</v>
+        <v>845582.437276</v>
       </c>
       <c r="P2" t="n">
-        <v>1243000</v>
+        <v>854000</v>
       </c>
       <c r="Q2" t="n">
-        <v>32758000</v>
+        <v>17896000</v>
       </c>
       <c r="R2" t="n">
-        <v>2334000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>1070000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>12557492</v>
+      </c>
+      <c r="T2" t="n">
+        <v>12557492</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.068</v>
+      </c>
       <c r="W2" t="n">
-        <v>1243000</v>
+        <v>854000</v>
       </c>
       <c r="X2" t="n">
-        <v>1243000</v>
+        <v>854000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1243000</v>
+        <v>854000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1244000</v>
+        <v>854000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1244000</v>
+        <v>854000</v>
       </c>
       <c r="AD2" t="n">
-        <v>621000</v>
+        <v>262000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1865000</v>
+        <v>1116000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-554000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-11000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>187000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>367000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-671000</v>
+        <v>-136000</v>
       </c>
       <c r="AL2" t="n">
-        <v>41000</v>
+        <v>60000</v>
       </c>
       <c r="AM2" t="n">
-        <v>922000</v>
+        <v>99000</v>
       </c>
       <c r="AN2" t="n">
-        <v>292000</v>
+        <v>23000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2950000</v>
+        <v>1120000</v>
       </c>
       <c r="AP2" t="n">
-        <v>20681000</v>
+        <v>9979000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5434000</v>
+        <v>2951000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3046000</v>
+        <v>1810000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2149000</v>
+        <v>1412000</v>
       </c>
       <c r="AT2" t="n">
-        <v>897000</v>
+        <v>398000</v>
       </c>
       <c r="AU2" t="n">
-        <v>102000</v>
+        <v>67000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3104000</v>
+        <v>1585000</v>
       </c>
       <c r="AW2" t="n">
-        <v>61000</v>
+        <v>25000</v>
       </c>
       <c r="AX2" t="n">
-        <v>3043000</v>
+        <v>1560000</v>
       </c>
       <c r="AY2" t="n">
-        <v>23631000</v>
+        <v>11099000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12077000</v>
+        <v>7917000</v>
       </c>
       <c r="BA2" t="n">
-        <v>35708000</v>
+        <v>19016000</v>
       </c>
       <c r="BB2" t="n">
-        <v>35708000</v>
+        <v>19016000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-170763.09795</v>
+        <v>-3146.414343</v>
       </c>
       <c r="C3" t="n">
-        <v>0.392559</v>
+        <v>0.349602</v>
       </c>
       <c r="D3" t="n">
-        <v>5207000</v>
+        <v>3246000</v>
       </c>
       <c r="E3" t="n">
-        <v>-435000</v>
+        <v>-9000</v>
       </c>
       <c r="F3" t="n">
-        <v>-435000</v>
+        <v>-9000</v>
       </c>
       <c r="G3" t="n">
-        <v>799000</v>
+        <v>653000</v>
       </c>
       <c r="H3" t="n">
-        <v>2503000</v>
+        <v>2007000</v>
       </c>
       <c r="I3" t="n">
-        <v>11769000</v>
+        <v>11861000</v>
       </c>
       <c r="J3" t="n">
-        <v>4772000</v>
+        <v>3237000</v>
       </c>
       <c r="K3" t="n">
-        <v>2269000</v>
+        <v>1230000</v>
       </c>
       <c r="L3" t="n">
-        <v>-826000</v>
+        <v>-265000</v>
       </c>
       <c r="M3" t="n">
-        <v>952000</v>
+        <v>226000</v>
       </c>
       <c r="N3" t="n">
-        <v>156000</v>
+        <v>45000</v>
       </c>
       <c r="O3" t="n">
-        <v>1063236.90205</v>
+        <v>658853.585657</v>
       </c>
       <c r="P3" t="n">
-        <v>799000</v>
+        <v>653000</v>
       </c>
       <c r="Q3" t="n">
-        <v>30132000</v>
+        <v>24792000</v>
       </c>
       <c r="R3" t="n">
-        <v>2148000</v>
+        <v>1201000</v>
       </c>
       <c r="S3" t="n">
-        <v>15869887</v>
+        <v>13740465</v>
       </c>
       <c r="T3" t="n">
-        <v>15869887</v>
+        <v>13740465</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0469</v>
+        <v>0.0083</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0469</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>799000</v>
+        <v>653000</v>
       </c>
       <c r="X3" t="n">
-        <v>799000</v>
+        <v>653000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>799000</v>
+        <v>653000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AB3" t="n">
-        <v>800000</v>
+        <v>653000</v>
       </c>
       <c r="AC3" t="n">
-        <v>800000</v>
+        <v>653000</v>
       </c>
       <c r="AD3" t="n">
-        <v>517000</v>
+        <v>351000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1317000</v>
+        <v>1004000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-435000</v>
+        <v>-9000</v>
       </c>
       <c r="AG3" t="n">
         <v>-2000</v>
       </c>
       <c r="AH3" t="n">
-        <v>83000</v>
+        <v>11000</v>
       </c>
       <c r="AI3" t="n">
-        <v>83000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>354000</v>
-      </c>
+        <v>11000</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>-826000</v>
+        <v>-265000</v>
       </c>
       <c r="AL3" t="n">
-        <v>30000</v>
+        <v>84000</v>
       </c>
       <c r="AM3" t="n">
-        <v>952000</v>
+        <v>226000</v>
       </c>
       <c r="AN3" t="n">
-        <v>156000</v>
+        <v>45000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2653000</v>
+        <v>1295000</v>
       </c>
       <c r="AP3" t="n">
-        <v>17380000</v>
+        <v>12931000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6111000</v>
+        <v>4539000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2486000</v>
+        <v>2007000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1681000</v>
+        <v>1490000</v>
       </c>
       <c r="AT3" t="n">
-        <v>805000</v>
+        <v>517000</v>
       </c>
       <c r="AU3" t="n">
-        <v>115000</v>
+        <v>48000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2138000</v>
+        <v>1942000</v>
       </c>
       <c r="AW3" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="AX3" t="n">
-        <v>2088000</v>
+        <v>1927000</v>
       </c>
       <c r="AY3" t="n">
-        <v>21016000</v>
+        <v>14226000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11769000</v>
+        <v>11861000</v>
       </c>
       <c r="BA3" t="n">
-        <v>32785000</v>
+        <v>26087000</v>
       </c>
       <c r="BB3" t="n">
-        <v>32785000</v>
+        <v>26087000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-3146.414343</v>
+        <v>-170763.09795</v>
       </c>
       <c r="C4" t="n">
-        <v>0.349602</v>
+        <v>0.392559</v>
       </c>
       <c r="D4" t="n">
-        <v>3246000</v>
+        <v>5207000</v>
       </c>
       <c r="E4" t="n">
-        <v>-9000</v>
+        <v>-435000</v>
       </c>
       <c r="F4" t="n">
-        <v>-9000</v>
+        <v>-435000</v>
       </c>
       <c r="G4" t="n">
-        <v>653000</v>
+        <v>799000</v>
       </c>
       <c r="H4" t="n">
-        <v>2007000</v>
+        <v>2503000</v>
       </c>
       <c r="I4" t="n">
-        <v>11861000</v>
+        <v>11769000</v>
       </c>
       <c r="J4" t="n">
-        <v>3237000</v>
+        <v>4772000</v>
       </c>
       <c r="K4" t="n">
-        <v>1230000</v>
+        <v>2269000</v>
       </c>
       <c r="L4" t="n">
-        <v>-265000</v>
+        <v>-826000</v>
       </c>
       <c r="M4" t="n">
-        <v>226000</v>
+        <v>952000</v>
       </c>
       <c r="N4" t="n">
-        <v>45000</v>
+        <v>156000</v>
       </c>
       <c r="O4" t="n">
-        <v>658853.585657</v>
+        <v>1063236.90205</v>
       </c>
       <c r="P4" t="n">
-        <v>653000</v>
+        <v>799000</v>
       </c>
       <c r="Q4" t="n">
-        <v>24792000</v>
+        <v>30132000</v>
       </c>
       <c r="R4" t="n">
-        <v>1201000</v>
+        <v>2148000</v>
       </c>
       <c r="S4" t="n">
-        <v>13740465</v>
+        <v>15869887</v>
       </c>
       <c r="T4" t="n">
-        <v>13740465</v>
+        <v>15869887</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0083</v>
+        <v>0.0469</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0469</v>
       </c>
       <c r="W4" t="n">
-        <v>653000</v>
+        <v>799000</v>
       </c>
       <c r="X4" t="n">
-        <v>653000</v>
+        <v>799000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>653000</v>
+        <v>799000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>653000</v>
+        <v>800000</v>
       </c>
       <c r="AC4" t="n">
-        <v>653000</v>
+        <v>800000</v>
       </c>
       <c r="AD4" t="n">
-        <v>351000</v>
+        <v>517000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1004000</v>
+        <v>1317000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-9000</v>
+        <v>-435000</v>
       </c>
       <c r="AG4" t="n">
         <v>-2000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11000</v>
+        <v>83000</v>
       </c>
       <c r="AI4" t="n">
-        <v>11000</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>83000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>354000</v>
+      </c>
       <c r="AK4" t="n">
-        <v>-265000</v>
+        <v>-826000</v>
       </c>
       <c r="AL4" t="n">
-        <v>84000</v>
+        <v>30000</v>
       </c>
       <c r="AM4" t="n">
-        <v>226000</v>
+        <v>952000</v>
       </c>
       <c r="AN4" t="n">
-        <v>45000</v>
+        <v>156000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1295000</v>
+        <v>2653000</v>
       </c>
       <c r="AP4" t="n">
-        <v>12931000</v>
+        <v>17380000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4539000</v>
+        <v>6111000</v>
       </c>
       <c r="AR4" t="n">
-        <v>2007000</v>
+        <v>2486000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1490000</v>
+        <v>1681000</v>
       </c>
       <c r="AT4" t="n">
-        <v>517000</v>
+        <v>805000</v>
       </c>
       <c r="AU4" t="n">
-        <v>48000</v>
+        <v>115000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1942000</v>
+        <v>2138000</v>
       </c>
       <c r="AW4" t="n">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1927000</v>
+        <v>2088000</v>
       </c>
       <c r="AY4" t="n">
-        <v>14226000</v>
+        <v>21016000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11861000</v>
+        <v>11769000</v>
       </c>
       <c r="BA4" t="n">
-        <v>26087000</v>
+        <v>32785000</v>
       </c>
       <c r="BB4" t="n">
-        <v>26087000</v>
+        <v>32785000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2582.437276</v>
+        <v>-184468.632708</v>
       </c>
       <c r="C5" t="n">
-        <v>0.234767</v>
+        <v>0.332976</v>
       </c>
       <c r="D5" t="n">
-        <v>3014000</v>
+        <v>6387000</v>
       </c>
       <c r="E5" t="n">
-        <v>11000</v>
+        <v>-554000</v>
       </c>
       <c r="F5" t="n">
-        <v>11000</v>
+        <v>-554000</v>
       </c>
       <c r="G5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
       <c r="H5" t="n">
-        <v>1810000</v>
+        <v>3046000</v>
       </c>
       <c r="I5" t="n">
-        <v>7917000</v>
+        <v>12077000</v>
       </c>
       <c r="J5" t="n">
-        <v>3025000</v>
+        <v>5833000</v>
       </c>
       <c r="K5" t="n">
-        <v>1215000</v>
+        <v>2787000</v>
       </c>
       <c r="L5" t="n">
-        <v>-136000</v>
+        <v>-671000</v>
       </c>
       <c r="M5" t="n">
-        <v>99000</v>
+        <v>922000</v>
       </c>
       <c r="N5" t="n">
-        <v>23000</v>
+        <v>292000</v>
       </c>
       <c r="O5" t="n">
-        <v>845582.437276</v>
+        <v>1612531.367292</v>
       </c>
       <c r="P5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
       <c r="Q5" t="n">
-        <v>17896000</v>
+        <v>32758000</v>
       </c>
       <c r="R5" t="n">
-        <v>1070000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>12557492</v>
-      </c>
-      <c r="T5" t="n">
-        <v>12557492</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0643</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.068</v>
-      </c>
+        <v>2334000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
       <c r="X5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>854000</v>
+        <v>1244000</v>
       </c>
       <c r="AC5" t="n">
-        <v>854000</v>
+        <v>1244000</v>
       </c>
       <c r="AD5" t="n">
-        <v>262000</v>
+        <v>621000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1116000</v>
+        <v>1865000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-11000</v>
-      </c>
+        <v>-554000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>187000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>367000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>-136000</v>
+        <v>-671000</v>
       </c>
       <c r="AL5" t="n">
-        <v>60000</v>
+        <v>41000</v>
       </c>
       <c r="AM5" t="n">
-        <v>99000</v>
+        <v>922000</v>
       </c>
       <c r="AN5" t="n">
-        <v>23000</v>
+        <v>292000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1120000</v>
+        <v>2950000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9979000</v>
+        <v>20681000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2951000</v>
+        <v>5434000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1810000</v>
+        <v>3046000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1412000</v>
+        <v>2149000</v>
       </c>
       <c r="AT5" t="n">
-        <v>398000</v>
+        <v>897000</v>
       </c>
       <c r="AU5" t="n">
-        <v>67000</v>
+        <v>102000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1585000</v>
+        <v>3104000</v>
       </c>
       <c r="AW5" t="n">
-        <v>25000</v>
+        <v>61000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1560000</v>
+        <v>3043000</v>
       </c>
       <c r="AY5" t="n">
-        <v>11099000</v>
+        <v>23631000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7917000</v>
+        <v>12077000</v>
       </c>
       <c r="BA5" t="n">
-        <v>19016000</v>
+        <v>35708000</v>
       </c>
       <c r="BB5" t="n">
-        <v>19016000</v>
+        <v>35708000</v>
       </c>
     </row>
   </sheetData>
@@ -1713,850 +1713,850 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>219000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>17405387</v>
+        <v>13634281</v>
       </c>
       <c r="D2" t="n">
-        <v>17624387</v>
+        <v>13634281</v>
       </c>
       <c r="E2" t="n">
-        <v>8017000</v>
+        <v>50000</v>
       </c>
       <c r="F2" t="n">
-        <v>16268000</v>
+        <v>6064000</v>
       </c>
       <c r="G2" t="n">
-        <v>18026000</v>
+        <v>14564000</v>
       </c>
       <c r="H2" t="n">
-        <v>43121000</v>
+        <v>25528000</v>
       </c>
       <c r="I2" t="n">
-        <v>21492000</v>
+        <v>16484000</v>
       </c>
       <c r="J2" t="n">
-        <v>18026000</v>
+        <v>14564000</v>
       </c>
       <c r="K2" t="n">
-        <v>975000</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>27828000</v>
+        <v>19464000</v>
       </c>
       <c r="M2" t="n">
-        <v>36440000</v>
+        <v>25528000</v>
       </c>
       <c r="N2" t="n">
-        <v>27829000</v>
+        <v>19465000</v>
       </c>
       <c r="O2" t="n">
         <v>1000</v>
       </c>
       <c r="P2" t="n">
-        <v>27828000</v>
-      </c>
-      <c r="Q2" t="n">
+        <v>19464000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>854000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8272000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5239000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5239000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>17767000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7123000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>572000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>198000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6064000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6064000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>288000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10644000</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1000</v>
       </c>
-      <c r="R2" t="n">
-        <v>1243000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13231000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>7234000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>7234000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>27761000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>11568000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>1153000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>521000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9350000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>738000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8612000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>546000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16193000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>6918000</v>
+        <v>2672000</v>
       </c>
       <c r="AI2" t="n">
-        <v>237000</v>
+        <v>30000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6681000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>2642000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>255000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>8715000</v>
+        <v>7889000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2586000</v>
+        <v>1358000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6129000</v>
+        <v>6531000</v>
       </c>
       <c r="AO2" t="n">
-        <v>55590000</v>
+        <v>37232000</v>
       </c>
       <c r="AP2" t="n">
-        <v>17905000</v>
+        <v>10105000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-9000</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>35000</v>
+        <v>28000</v>
       </c>
       <c r="AS2" t="n">
-        <v>852000</v>
+        <v>948000</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>9802000</v>
+        <v>4900000</v>
       </c>
       <c r="AV2" t="n">
-        <v>9224000</v>
+        <v>4900000</v>
       </c>
       <c r="AW2" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>6905000</v>
+        <v>3845000</v>
       </c>
       <c r="AY2" t="n">
-        <v>6906000</v>
+        <v>3845000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1128000</v>
+        <v>513000</v>
       </c>
       <c r="BA2" t="n">
-        <v>303000</v>
+        <v>352000</v>
       </c>
       <c r="BB2" t="n">
-        <v>5475000</v>
+        <v>2980000</v>
       </c>
       <c r="BC2" t="n">
-        <v>37685000</v>
+        <v>27128000</v>
       </c>
       <c r="BD2" t="n">
-        <v>2354000</v>
+        <v>3307000</v>
       </c>
       <c r="BE2" t="n">
-        <v>19000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>299000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
-        <v>202000</v>
+        <v>323000</v>
       </c>
       <c r="BH2" t="n">
-        <v>8636000</v>
+        <v>7184000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-629000</v>
+        <v>-308000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>108000</v>
+        <v>20000</v>
       </c>
       <c r="BL2" t="n">
-        <v>2020000</v>
+        <v>2572000</v>
       </c>
       <c r="BM2" t="n">
-        <v>7138000</v>
+        <v>4899000</v>
       </c>
       <c r="BN2" t="n">
-        <v>210000</v>
+        <v>100000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1363000</v>
+        <v>1982000</v>
       </c>
       <c r="BP2" t="n">
-        <v>8318000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
+        <v>5572000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-128000</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>5572000</v>
+      </c>
       <c r="BS2" t="n">
-        <v>16284000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>9008000</v>
-      </c>
+        <v>8656000</v>
+      </c>
+      <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="n">
-        <v>7276000</v>
+        <v>8656000</v>
       </c>
       <c r="BV2" t="n">
-        <v>7276000</v>
+        <v>8656000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>17623887</v>
+        <v>13794935</v>
       </c>
       <c r="D3" t="n">
-        <v>17623887</v>
+        <v>13794935</v>
       </c>
       <c r="E3" t="n">
-        <v>11380000</v>
+        <v>10644000</v>
       </c>
       <c r="F3" t="n">
-        <v>18406000</v>
+        <v>19106000</v>
       </c>
       <c r="G3" t="n">
-        <v>16658000</v>
+        <v>11493000</v>
       </c>
       <c r="H3" t="n">
-        <v>45341000</v>
+        <v>39758000</v>
       </c>
       <c r="I3" t="n">
-        <v>20496000</v>
+        <v>18609000</v>
       </c>
       <c r="J3" t="n">
-        <v>16658000</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>11493000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>55000</v>
+      </c>
       <c r="L3" t="n">
-        <v>26935000</v>
+        <v>20652000</v>
       </c>
       <c r="M3" t="n">
-        <v>37723000</v>
+        <v>34044000</v>
       </c>
       <c r="N3" t="n">
-        <v>26936000</v>
+        <v>20597000</v>
       </c>
       <c r="O3" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20652000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>656000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8633000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5319000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5319000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>32569000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15672000</v>
+      </c>
+      <c r="X3" t="n">
         <v>1000</v>
       </c>
-      <c r="P3" t="n">
-        <v>26935000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>799000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>13230000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7233000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>7233000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>31275000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>1226000</v>
+        <v>1104000</v>
       </c>
       <c r="AA3" t="n">
-        <v>546000</v>
+        <v>563000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10788000</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>13392000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>55000</v>
+      </c>
       <c r="AD3" t="n">
-        <v>10788000</v>
+        <v>13392000</v>
       </c>
       <c r="AE3" t="n">
-        <v>440000</v>
+        <v>613000</v>
       </c>
       <c r="AF3" t="n">
-        <v>18275000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>16897000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>806000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>7618000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>5714000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>253000</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>7618000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>5714000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>395000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>9761000</v>
+        <v>10460000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2182000</v>
+        <v>2550000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7579000</v>
+        <v>7910000</v>
       </c>
       <c r="AO3" t="n">
-        <v>58211000</v>
+        <v>53166000</v>
       </c>
       <c r="AP3" t="n">
-        <v>19439000</v>
+        <v>17660000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2000</v>
+        <v>16000</v>
       </c>
       <c r="AR3" t="n">
-        <v>39000</v>
+        <v>41000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1130000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>984000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>452000</v>
+      </c>
       <c r="AU3" t="n">
-        <v>10277000</v>
+        <v>9159000</v>
       </c>
       <c r="AV3" t="n">
-        <v>9699000</v>
+        <v>8581000</v>
       </c>
       <c r="AW3" t="n">
         <v>578000</v>
       </c>
       <c r="AX3" t="n">
-        <v>7600000</v>
+        <v>7065000</v>
       </c>
       <c r="AY3" t="n">
-        <v>7600000</v>
+        <v>7065000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1372000</v>
+        <v>896000</v>
       </c>
       <c r="BA3" t="n">
-        <v>387000</v>
+        <v>423000</v>
       </c>
       <c r="BB3" t="n">
-        <v>5841000</v>
+        <v>5746000</v>
       </c>
       <c r="BC3" t="n">
-        <v>38771000</v>
+        <v>35506000</v>
       </c>
       <c r="BD3" t="n">
-        <v>2286000</v>
+        <v>2453000</v>
       </c>
       <c r="BE3" t="n">
-        <v>87000</v>
+        <v>107000</v>
       </c>
       <c r="BF3" t="n">
-        <v>342000</v>
+        <v>373000</v>
       </c>
       <c r="BG3" t="n">
-        <v>334000</v>
+        <v>151000</v>
       </c>
       <c r="BH3" t="n">
-        <v>10671000</v>
+        <v>10032000</v>
       </c>
       <c r="BI3" t="n">
-        <v>-456000</v>
+        <v>-326000</v>
       </c>
       <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>98000</v>
+        <v>42000</v>
       </c>
       <c r="BL3" t="n">
-        <v>3090000</v>
+        <v>3134000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7939000</v>
+        <v>7182000</v>
       </c>
       <c r="BN3" t="n">
-        <v>398000</v>
+        <v>387000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1274000</v>
+        <v>2300000</v>
       </c>
       <c r="BP3" t="n">
-        <v>11206000</v>
+        <v>11241000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-302000</v>
+        <v>-313000</v>
       </c>
       <c r="BR3" t="n">
-        <v>11206000</v>
+        <v>11241000</v>
       </c>
       <c r="BS3" t="n">
-        <v>12173000</v>
+        <v>8462000</v>
       </c>
       <c r="BT3" t="n">
-        <v>5147000</v>
+        <v>2755000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7026000</v>
+        <v>8462000</v>
       </c>
       <c r="BV3" t="n">
-        <v>7026000</v>
+        <v>8462000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>13794935</v>
+        <v>17623887</v>
       </c>
       <c r="D4" t="n">
-        <v>13794935</v>
+        <v>17623887</v>
       </c>
       <c r="E4" t="n">
-        <v>10644000</v>
+        <v>11380000</v>
       </c>
       <c r="F4" t="n">
-        <v>19106000</v>
+        <v>18406000</v>
       </c>
       <c r="G4" t="n">
-        <v>11493000</v>
+        <v>16658000</v>
       </c>
       <c r="H4" t="n">
-        <v>39758000</v>
+        <v>45341000</v>
       </c>
       <c r="I4" t="n">
-        <v>18609000</v>
+        <v>20496000</v>
       </c>
       <c r="J4" t="n">
-        <v>11493000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>55000</v>
-      </c>
+        <v>16658000</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>20652000</v>
+        <v>26935000</v>
       </c>
       <c r="M4" t="n">
-        <v>34044000</v>
+        <v>37723000</v>
       </c>
       <c r="N4" t="n">
-        <v>20597000</v>
+        <v>26936000</v>
       </c>
       <c r="O4" t="n">
-        <v>-55000</v>
+        <v>1000</v>
       </c>
       <c r="P4" t="n">
-        <v>20652000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>26935000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1000</v>
+      </c>
       <c r="R4" t="n">
-        <v>656000</v>
+        <v>799000</v>
       </c>
       <c r="S4" t="n">
-        <v>8633000</v>
+        <v>13230000</v>
       </c>
       <c r="T4" t="n">
-        <v>5319000</v>
+        <v>7233000</v>
       </c>
       <c r="U4" t="n">
-        <v>5319000</v>
+        <v>7233000</v>
       </c>
       <c r="V4" t="n">
-        <v>32569000</v>
+        <v>31275000</v>
       </c>
       <c r="W4" t="n">
-        <v>15672000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>13000000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>1104000</v>
+        <v>1226000</v>
       </c>
       <c r="AA4" t="n">
-        <v>563000</v>
+        <v>546000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13392000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>55000</v>
-      </c>
+        <v>10788000</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>13392000</v>
+        <v>10788000</v>
       </c>
       <c r="AE4" t="n">
-        <v>613000</v>
+        <v>440000</v>
       </c>
       <c r="AF4" t="n">
-        <v>16897000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>806000</v>
-      </c>
+        <v>18275000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>5714000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>253000</v>
-      </c>
+        <v>7618000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>5714000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>395000</v>
-      </c>
+        <v>7618000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>10460000</v>
+        <v>9761000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2550000</v>
+        <v>2182000</v>
       </c>
       <c r="AN4" t="n">
-        <v>7910000</v>
+        <v>7579000</v>
       </c>
       <c r="AO4" t="n">
-        <v>53166000</v>
+        <v>58211000</v>
       </c>
       <c r="AP4" t="n">
-        <v>17660000</v>
+        <v>19439000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16000</v>
+        <v>-2000</v>
       </c>
       <c r="AR4" t="n">
-        <v>41000</v>
+        <v>39000</v>
       </c>
       <c r="AS4" t="n">
-        <v>984000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>452000</v>
-      </c>
+        <v>1130000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>9159000</v>
+        <v>10277000</v>
       </c>
       <c r="AV4" t="n">
-        <v>8581000</v>
+        <v>9699000</v>
       </c>
       <c r="AW4" t="n">
         <v>578000</v>
       </c>
       <c r="AX4" t="n">
-        <v>7065000</v>
+        <v>7600000</v>
       </c>
       <c r="AY4" t="n">
-        <v>7065000</v>
+        <v>7600000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>896000</v>
+        <v>1372000</v>
       </c>
       <c r="BA4" t="n">
-        <v>423000</v>
+        <v>387000</v>
       </c>
       <c r="BB4" t="n">
-        <v>5746000</v>
+        <v>5841000</v>
       </c>
       <c r="BC4" t="n">
-        <v>35506000</v>
+        <v>38771000</v>
       </c>
       <c r="BD4" t="n">
-        <v>2453000</v>
+        <v>2286000</v>
       </c>
       <c r="BE4" t="n">
-        <v>107000</v>
+        <v>87000</v>
       </c>
       <c r="BF4" t="n">
-        <v>373000</v>
+        <v>342000</v>
       </c>
       <c r="BG4" t="n">
-        <v>151000</v>
+        <v>334000</v>
       </c>
       <c r="BH4" t="n">
-        <v>10032000</v>
+        <v>10671000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-326000</v>
+        <v>-456000</v>
       </c>
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="n">
-        <v>42000</v>
+        <v>98000</v>
       </c>
       <c r="BL4" t="n">
-        <v>3134000</v>
+        <v>3090000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7182000</v>
+        <v>7939000</v>
       </c>
       <c r="BN4" t="n">
-        <v>387000</v>
+        <v>398000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2300000</v>
+        <v>1274000</v>
       </c>
       <c r="BP4" t="n">
-        <v>11241000</v>
+        <v>11206000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-313000</v>
+        <v>-302000</v>
       </c>
       <c r="BR4" t="n">
-        <v>11241000</v>
+        <v>11206000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8462000</v>
+        <v>12173000</v>
       </c>
       <c r="BT4" t="n">
-        <v>2755000</v>
+        <v>5147000</v>
       </c>
       <c r="BU4" t="n">
-        <v>8462000</v>
+        <v>7026000</v>
       </c>
       <c r="BV4" t="n">
-        <v>8462000</v>
+        <v>7026000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>219000</v>
+      </c>
       <c r="C5" t="n">
-        <v>13634281</v>
+        <v>17405387</v>
       </c>
       <c r="D5" t="n">
-        <v>13634281</v>
+        <v>17624387</v>
       </c>
       <c r="E5" t="n">
-        <v>50000</v>
+        <v>8017000</v>
       </c>
       <c r="F5" t="n">
-        <v>6064000</v>
+        <v>16268000</v>
       </c>
       <c r="G5" t="n">
-        <v>14564000</v>
+        <v>18026000</v>
       </c>
       <c r="H5" t="n">
-        <v>25528000</v>
+        <v>43121000</v>
       </c>
       <c r="I5" t="n">
-        <v>16484000</v>
+        <v>21492000</v>
       </c>
       <c r="J5" t="n">
-        <v>14564000</v>
+        <v>18026000</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>975000</v>
       </c>
       <c r="L5" t="n">
-        <v>19464000</v>
+        <v>27828000</v>
       </c>
       <c r="M5" t="n">
-        <v>25528000</v>
+        <v>36440000</v>
       </c>
       <c r="N5" t="n">
-        <v>19465000</v>
+        <v>27829000</v>
       </c>
       <c r="O5" t="n">
         <v>1000</v>
       </c>
       <c r="P5" t="n">
-        <v>19464000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>27828000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1000</v>
+      </c>
       <c r="R5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
       <c r="S5" t="n">
-        <v>8272000</v>
+        <v>13231000</v>
       </c>
       <c r="T5" t="n">
-        <v>5239000</v>
+        <v>7234000</v>
       </c>
       <c r="U5" t="n">
-        <v>5239000</v>
+        <v>7234000</v>
       </c>
       <c r="V5" t="n">
-        <v>17767000</v>
+        <v>27761000</v>
       </c>
       <c r="W5" t="n">
-        <v>7123000</v>
+        <v>11568000</v>
       </c>
       <c r="X5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2000</v>
-      </c>
+        <v>-2000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>572000</v>
+        <v>1153000</v>
       </c>
       <c r="AA5" t="n">
-        <v>198000</v>
+        <v>521000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6064000</v>
+        <v>9350000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>738000</v>
       </c>
       <c r="AD5" t="n">
-        <v>6064000</v>
+        <v>8612000</v>
       </c>
       <c r="AE5" t="n">
-        <v>288000</v>
+        <v>546000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10644000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
+        <v>16193000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>2672000</v>
+        <v>6918000</v>
       </c>
       <c r="AI5" t="n">
-        <v>30000</v>
+        <v>237000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2642000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>255000</v>
-      </c>
+        <v>6681000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>7889000</v>
+        <v>8715000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1358000</v>
+        <v>2586000</v>
       </c>
       <c r="AN5" t="n">
-        <v>6531000</v>
+        <v>6129000</v>
       </c>
       <c r="AO5" t="n">
-        <v>37232000</v>
+        <v>55590000</v>
       </c>
       <c r="AP5" t="n">
-        <v>10105000</v>
+        <v>17905000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1000</v>
+        <v>-9000</v>
       </c>
       <c r="AR5" t="n">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="AS5" t="n">
-        <v>948000</v>
+        <v>852000</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>4900000</v>
+        <v>9802000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4900000</v>
+        <v>9224000</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>578000</v>
       </c>
       <c r="AX5" t="n">
-        <v>3845000</v>
+        <v>6905000</v>
       </c>
       <c r="AY5" t="n">
-        <v>3845000</v>
+        <v>6906000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>513000</v>
+        <v>1128000</v>
       </c>
       <c r="BA5" t="n">
-        <v>352000</v>
+        <v>303000</v>
       </c>
       <c r="BB5" t="n">
-        <v>2980000</v>
+        <v>5475000</v>
       </c>
       <c r="BC5" t="n">
-        <v>27128000</v>
+        <v>37685000</v>
       </c>
       <c r="BD5" t="n">
-        <v>3307000</v>
+        <v>2354000</v>
       </c>
       <c r="BE5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>19000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>299000</v>
+      </c>
       <c r="BG5" t="n">
-        <v>323000</v>
+        <v>202000</v>
       </c>
       <c r="BH5" t="n">
-        <v>7184000</v>
+        <v>8636000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-308000</v>
+        <v>-629000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>20000</v>
+        <v>108000</v>
       </c>
       <c r="BL5" t="n">
-        <v>2572000</v>
+        <v>2020000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4899000</v>
+        <v>7138000</v>
       </c>
       <c r="BN5" t="n">
-        <v>100000</v>
+        <v>210000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1982000</v>
+        <v>1363000</v>
       </c>
       <c r="BP5" t="n">
-        <v>5572000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-128000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>5572000</v>
-      </c>
+        <v>8318000</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>8656000</v>
-      </c>
-      <c r="BT5" t="inlineStr"/>
+        <v>16284000</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>9008000</v>
+      </c>
       <c r="BU5" t="n">
-        <v>8656000</v>
+        <v>7276000</v>
       </c>
       <c r="BV5" t="n">
-        <v>8656000</v>
+        <v>7276000</v>
       </c>
     </row>
   </sheetData>
@@ -2742,56 +2742,46 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>4729000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-314000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
+        <v>-3709000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-1565000</v>
+        <v>-2431000</v>
       </c>
       <c r="F2" t="n">
-        <v>7276000</v>
+        <v>8656000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>7026000</v>
+        <v>10379000</v>
       </c>
       <c r="I2" t="n">
-        <v>250000</v>
+        <v>-1723000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2447000</v>
+        <v>2011000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2133000</v>
+        <v>-2151000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-314000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-314000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
+        <v>4162000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-3597000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-2032000</v>
-      </c>
+        <v>-2456000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2800,284 +2790,294 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-1179000</v>
+        <v>-2010000</v>
       </c>
       <c r="V2" t="n">
-        <v>-386000</v>
+        <v>-421000</v>
       </c>
       <c r="W2" t="n">
-        <v>6294000</v>
+        <v>-1278000</v>
       </c>
       <c r="X2" t="n">
-        <v>1440000</v>
+        <v>-4370000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-186000</v>
+        <v>530000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1553000</v>
+        <v>-2928000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1448000</v>
+        <v>1809000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1860000</v>
+        <v>-3155000</v>
       </c>
       <c r="AC2" t="n">
-        <v>3023000</v>
+        <v>-248000</v>
       </c>
       <c r="AD2" t="n">
-        <v>80000</v>
+        <v>174000</v>
       </c>
       <c r="AE2" t="n">
-        <v>3046000</v>
+        <v>1810000</v>
       </c>
       <c r="AF2" t="n">
-        <v>3046000</v>
+        <v>1810000</v>
       </c>
       <c r="AG2" t="n">
-        <v>484000</v>
+        <v>255000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1243000</v>
+        <v>854000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1225000</v>
+        <v>-2859000</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>5628000</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-4122000</v>
+        <v>-3106000</v>
       </c>
       <c r="F3" t="n">
-        <v>7026000</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>8462000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-4021000</v>
+      </c>
       <c r="H3" t="n">
-        <v>8462000</v>
+        <v>8656000</v>
       </c>
       <c r="I3" t="n">
-        <v>-1436000</v>
+        <v>3827000</v>
       </c>
       <c r="J3" t="n">
-        <v>4918000</v>
+        <v>3580000</v>
       </c>
       <c r="K3" t="n">
-        <v>-710000</v>
+        <v>3594000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5628000</v>
+        <v>-14000</v>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>5628000</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-9251000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5129000</v>
+        <v>4029000</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-923000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-923000</v>
       </c>
       <c r="U3" t="n">
-        <v>-2824000</v>
+        <v>-2415000</v>
       </c>
       <c r="V3" t="n">
-        <v>-1298000</v>
+        <v>-691000</v>
       </c>
       <c r="W3" t="n">
-        <v>2897000</v>
+        <v>247000</v>
       </c>
       <c r="X3" t="n">
-        <v>-824000</v>
+        <v>-2879000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-537000</v>
+        <v>363000</v>
       </c>
       <c r="Z3" t="n">
-        <v>136000</v>
+        <v>741000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-334000</v>
+        <v>299000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-768000</v>
+        <v>-1156000</v>
       </c>
       <c r="AC3" t="n">
-        <v>961000</v>
+        <v>-2856000</v>
       </c>
       <c r="AD3" t="n">
-        <v>33000</v>
+        <v>129000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2503000</v>
+        <v>2007000</v>
       </c>
       <c r="AF3" t="n">
-        <v>2503000</v>
+        <v>2007000</v>
       </c>
       <c r="AG3" t="n">
-        <v>388000</v>
+        <v>333000</v>
       </c>
       <c r="AH3" t="n">
-        <v>798000</v>
+        <v>656000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2859000</v>
+        <v>-1225000</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>5628000</v>
+      </c>
       <c r="E4" t="n">
-        <v>-3106000</v>
+        <v>-4122000</v>
       </c>
       <c r="F4" t="n">
+        <v>7026000</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>8462000</v>
       </c>
-      <c r="G4" t="n">
-        <v>-4021000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8656000</v>
-      </c>
       <c r="I4" t="n">
-        <v>3827000</v>
+        <v>-1436000</v>
       </c>
       <c r="J4" t="n">
-        <v>3580000</v>
+        <v>4918000</v>
       </c>
       <c r="K4" t="n">
-        <v>3594000</v>
+        <v>-710000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-14000</v>
+        <v>5628000</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>5628000</v>
+      </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-9251000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4029000</v>
+        <v>-5129000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-923000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-923000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-2415000</v>
+        <v>-2824000</v>
       </c>
       <c r="V4" t="n">
-        <v>-691000</v>
+        <v>-1298000</v>
       </c>
       <c r="W4" t="n">
-        <v>247000</v>
+        <v>2897000</v>
       </c>
       <c r="X4" t="n">
-        <v>-2879000</v>
+        <v>-824000</v>
       </c>
       <c r="Y4" t="n">
-        <v>363000</v>
+        <v>-537000</v>
       </c>
       <c r="Z4" t="n">
-        <v>741000</v>
+        <v>136000</v>
       </c>
       <c r="AA4" t="n">
-        <v>299000</v>
+        <v>-334000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1156000</v>
+        <v>-768000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2856000</v>
+        <v>961000</v>
       </c>
       <c r="AD4" t="n">
-        <v>129000</v>
+        <v>33000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2007000</v>
+        <v>2503000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2007000</v>
+        <v>2503000</v>
       </c>
       <c r="AG4" t="n">
-        <v>333000</v>
+        <v>388000</v>
       </c>
       <c r="AH4" t="n">
-        <v>656000</v>
+        <v>798000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3709000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+        <v>4729000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-314000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
-        <v>-2431000</v>
+        <v>-1565000</v>
       </c>
       <c r="F5" t="n">
-        <v>8656000</v>
+        <v>7276000</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>10379000</v>
+        <v>7026000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1723000</v>
+        <v>250000</v>
       </c>
       <c r="J5" t="n">
-        <v>2011000</v>
+        <v>-2447000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2151000</v>
+        <v>-2133000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4162000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-314000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-314000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
-        <v>-2456000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>-3597000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-2032000</v>
+      </c>
       <c r="R5" t="n">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -3086,46 +3086,46 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-2010000</v>
+        <v>-1179000</v>
       </c>
       <c r="V5" t="n">
-        <v>-421000</v>
+        <v>-386000</v>
       </c>
       <c r="W5" t="n">
-        <v>-1278000</v>
+        <v>6294000</v>
       </c>
       <c r="X5" t="n">
-        <v>-4370000</v>
+        <v>1440000</v>
       </c>
       <c r="Y5" t="n">
-        <v>530000</v>
+        <v>-186000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2928000</v>
+        <v>-1553000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1809000</v>
+        <v>-1448000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3155000</v>
+        <v>1860000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-248000</v>
+        <v>3023000</v>
       </c>
       <c r="AD5" t="n">
-        <v>174000</v>
+        <v>80000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1810000</v>
+        <v>3046000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1810000</v>
+        <v>3046000</v>
       </c>
       <c r="AG5" t="n">
-        <v>255000</v>
+        <v>484000</v>
       </c>
       <c r="AH5" t="n">
-        <v>854000</v>
+        <v>1243000</v>
       </c>
     </row>
   </sheetData>
@@ -3590,172 +3590,172 @@
       </c>
       <c r="CL1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="DT1" t="inlineStr">
@@ -3855,7 +3855,7 @@
         <v>3.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.856</v>
+        <v>0.84</v>
       </c>
       <c r="AA2" t="n">
         <v>25.75</v>
@@ -3965,7 +3965,7 @@
         <v>1.109215</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -4068,129 +4068,129 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>ELES SEMICONDUCTOR EQUIPMENT SA</t>
+          <t>PREPRE</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>ELES Semiconductor Equipment S.p.A.</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="CN2" t="n">
+        <v>0</v>
+      </c>
       <c r="CO2" t="n">
-        <v>1776751506</v>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>finmb_46722658</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
+        <v>3.09</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-0.016600132</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-0.0053435047</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.42564988</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.1597575</v>
       </c>
       <c r="CT2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>15</v>
       </c>
       <c r="CV2" t="b">
         <v>0</v>
       </c>
       <c r="CW2" t="n">
+        <v>1776751506</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>finmb_46722658</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DD2" t="b">
         <v>0</v>
       </c>
-      <c r="CX2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="CY2" t="b">
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DF2" t="n">
         <v>1613372400000</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>ELES Semiconductor Equipment S.p.A.</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
         <v>0</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>3.09 - 3.09</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="DK2" t="n">
         <v>48</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DL2" t="n">
         <v>1.6949999</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DM2" t="n">
         <v>1.2150537</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>1.395 - 3.27</t>
         </is>
       </c>
-      <c r="DH2" t="n">
+      <c r="DO2" t="n">
         <v>-0.18000007</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DP2" t="n">
         <v>-0.05504589</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DQ2" t="n">
         <v>110.9215</v>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>ELES SEMICONDUCTOR EQUIPMENT SA</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
         <v>0.12</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.016600132</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.0053435047</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.42564988</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.1597575</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
       </c>
       <c r="DT2" t="inlineStr"/>
     </row>
